--- a/Project Documentation/Test Report - April 2026.xlsx
+++ b/Project Documentation/Test Report - April 2026.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>Bug ID</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>JIRA Link</t>
   </si>
   <si>
@@ -25,30 +28,51 @@
     <t>CTB-226</t>
   </si>
   <si>
+    <t xml:space="preserve">User authentication : Auto Log off </t>
+  </si>
+  <si>
     <t>Passed</t>
   </si>
   <si>
     <t>CTB-227</t>
   </si>
   <si>
+    <t>Favicon missing</t>
+  </si>
+  <si>
     <t>Failed</t>
   </si>
   <si>
     <t>CTB-228</t>
   </si>
   <si>
+    <t>Update all rights reserved year to 2026</t>
+  </si>
+  <si>
     <t>CTB-229</t>
   </si>
   <si>
+    <t>Negative values in fields</t>
+  </si>
+  <si>
     <t>CTB-230</t>
   </si>
   <si>
+    <t>No data in History Tab</t>
+  </si>
+  <si>
     <t>CTB-231</t>
   </si>
   <si>
+    <t>No links in the social icons in footer</t>
+  </si>
+  <si>
     <t>CTB-232</t>
   </si>
   <si>
+    <t>Stop loss and Take Profit fields should be percentage fieds</t>
+  </si>
+  <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-232</t>
   </si>
   <si>
@@ -58,6 +82,9 @@
     <t>CTB-233</t>
   </si>
   <si>
+    <t xml:space="preserve">News Page: Error in fetching the news </t>
+  </si>
+  <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-233</t>
   </si>
   <si>
@@ -67,22 +94,34 @@
     <t>CTB-234</t>
   </si>
   <si>
+    <t>Trades Page : Put proper labels for variables</t>
+  </si>
+  <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-234</t>
   </si>
   <si>
     <t>CTB-235</t>
   </si>
   <si>
+    <t>Market Data: Add Missing Currency ( $) Percentage (%) symbols in columns</t>
+  </si>
+  <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-235</t>
   </si>
   <si>
     <t>CTB-236</t>
   </si>
   <si>
+    <t>Market Data: Add Dollar and Percentage where appropriate in table</t>
+  </si>
+  <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-236</t>
   </si>
   <si>
     <t>CTB-237</t>
+  </si>
+  <si>
+    <t>History Data: Fix the comment column values to appropriate labels</t>
   </si>
   <si>
     <t>https://aliasadsqa.atlassian.net/browse/CTB-237</t>
@@ -92,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -132,6 +171,11 @@
       <u/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -159,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -169,6 +213,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -180,11 +227,17 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -406,7 +459,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="41.5"/>
+    <col customWidth="1" min="2" max="2" width="62.38"/>
+    <col customWidth="1" min="3" max="3" width="41.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,286 +473,331 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <f t="shared" ref="B2:B7" si="1">CONCATENATE("https://aliasadsqa.atlassian.net/browse/",A2)</f>
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="str">
+        <f t="shared" ref="C2:C7" si="1">CONCATENATE("https://aliasadsqa.atlassian.net/browse/",A2)</f>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-226</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="5" t="str">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="str">
         <f t="shared" si="1"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-227</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>6</v>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6" t="str">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="str">
         <f t="shared" si="1"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-228</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="str">
         <f t="shared" si="1"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-229</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="8" t="str">
         <f t="shared" si="1"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-230</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="7" t="str">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="8" t="str">
         <f t="shared" si="1"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-231</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>4</v>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
-        <v>13</v>
+      <c r="A9" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="3" t="str">
-        <f t="shared" ref="B10:B11" si="2">CONCATENATE("https://aliasadsqa.atlassian.net/browse/",A10)</f>
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f t="shared" ref="C10:C11" si="2">CONCATENATE("https://aliasadsqa.atlassian.net/browse/",A10)</f>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-227</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="str">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="str">
         <f t="shared" si="2"/>
         <v>https://aliasadsqa.atlassian.net/browse/CTB-228</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="13"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="10"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="13"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="10"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="13"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="10"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="13"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="10"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="13"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="10"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="13"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="10"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="13"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="10"/>
-      <c r="C25" s="2"/>
+      <c r="A25" s="13"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="10"/>
-      <c r="C26" s="2"/>
+      <c r="A26" s="13"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="10"/>
-      <c r="C27" s="2"/>
+      <c r="A27" s="13"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="10"/>
-      <c r="C28" s="2"/>
+      <c r="A28" s="13"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="10"/>
-      <c r="C29" s="2"/>
+      <c r="A29" s="13"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="10"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="13"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="10"/>
-      <c r="C31" s="2"/>
+      <c r="A31" s="13"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="10"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="13"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="10"/>
-      <c r="C33" s="2"/>
+      <c r="A33" s="13"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="10"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="13"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="10"/>
-      <c r="C35" s="2"/>
+      <c r="A35" s="13"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36">
-      <c r="A36" s="10"/>
-      <c r="C36" s="2"/>
+      <c r="A36" s="13"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37">
-      <c r="A37" s="10"/>
-      <c r="C37" s="2"/>
+      <c r="A37" s="13"/>
+      <c r="D37" s="2"/>
     </row>
     <row r="38">
-      <c r="A38" s="10"/>
-      <c r="C38" s="2"/>
+      <c r="A38" s="13"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" s="10"/>
-      <c r="C39" s="2"/>
+      <c r="A39" s="13"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40">
-      <c r="A40" s="10"/>
-      <c r="C40" s="2"/>
+      <c r="A40" s="13"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41">
-      <c r="A41" s="10"/>
-      <c r="C41" s="2"/>
+      <c r="A41" s="13"/>
+      <c r="D41" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C8 C10:C16">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D8 D10:D16">
       <formula1>"Failed,Passed,Open"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B8"/>
-    <hyperlink r:id="rId2" ref="B12"/>
-    <hyperlink r:id="rId3" ref="B13"/>
-    <hyperlink r:id="rId4" ref="B14"/>
-    <hyperlink r:id="rId5" ref="B15"/>
-    <hyperlink r:id="rId6" ref="B16"/>
+    <hyperlink r:id="rId1" ref="C8"/>
+    <hyperlink r:id="rId2" ref="C12"/>
+    <hyperlink r:id="rId3" ref="C13"/>
+    <hyperlink r:id="rId4" ref="C14"/>
+    <hyperlink r:id="rId5" ref="C15"/>
+    <hyperlink r:id="rId6" ref="C16"/>
   </hyperlinks>
   <drawing r:id="rId7"/>
 </worksheet>
